--- a/results/Int Task Remove ACC 0.9/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.9/Linea_fi_explain.xlsx
@@ -1172,7 +1172,7 @@
         <v>-0.0004578156037353209</v>
       </c>
       <c r="J3" t="n">
-        <v>3.502371062826135e-05</v>
+        <v>3.011211927266165e-05</v>
       </c>
       <c r="K3" t="n">
         <v>0.005121891064307381</v>
@@ -1187,7 +1187,7 @@
         <v>0.02632802513064613</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01983547448437776</v>
+        <v>0.01984081921981335</v>
       </c>
       <c r="P3" t="n">
         <v>0.02977190690094626</v>
@@ -1196,7 +1196,7 @@
         <v>-0.001287144315466272</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008268014932435669</v>
+        <v>0.008295260869794683</v>
       </c>
       <c r="S3" t="n">
         <v>0.3729205183192228</v>
@@ -1208,7 +1208,7 @@
         <v>0.3205680809310777</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0004639911642745231</v>
+        <v>-0.0004578156037353209</v>
       </c>
       <c r="W3" t="n">
         <v>0.0008057302357048945</v>
@@ -1232,7 +1232,7 @@
         <v>0.0460034597289818</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1140093391609549</v>
+        <v>0.1140044275695992</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2884019295997374</v>
@@ -1253,7 +1253,7 @@
         <v>0.06982423464129442</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.06405622754656314</v>
+        <v>0.06406225164294868</v>
       </c>
       <c r="AL3" t="n">
         <v>-0.0002257210535899178</v>
@@ -1298,7 +1298,7 @@
         <v>0.005022971103573993</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0003439953239137872</v>
+        <v>0.0003494777800541383</v>
       </c>
       <c r="BA3" t="n">
         <v>-0.001524657219638915</v>
@@ -1316,7 +1316,7 @@
         <v>-0.005220137379163469</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.003916750842068993</v>
+        <v>0.00392209557750459</v>
       </c>
       <c r="BG3" t="n">
         <v>0.009360184720548802</v>
@@ -1428,7 +1428,7 @@
         <v>0.03556214174389404</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02820294716931285</v>
+        <v>0.02822104144623354</v>
       </c>
       <c r="F4" t="n">
         <v>0.01382970965129832</v>
@@ -1443,7 +1443,7 @@
         <v>0.0006222588008288251</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002468586753494513</v>
+        <v>0.002466323223930201</v>
       </c>
       <c r="K4" t="n">
         <v>0.02247172530353948</v>
@@ -1458,7 +1458,7 @@
         <v>0.031750708737132</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02249274787264945</v>
+        <v>0.02249608252749439</v>
       </c>
       <c r="P4" t="n">
         <v>0.04165863237555419</v>
@@ -1467,7 +1467,7 @@
         <v>0.005249980578870751</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02216766335185549</v>
+        <v>0.02214832560974879</v>
       </c>
       <c r="S4" t="n">
         <v>0.1207984264440671</v>
@@ -1479,7 +1479,7 @@
         <v>0.1191748347030521</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0006408968326904453</v>
+        <v>0.0006222588008288251</v>
       </c>
       <c r="W4" t="n">
         <v>0.002729823830451014</v>
@@ -1503,7 +1503,7 @@
         <v>0.05532485222131515</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.09507122164445607</v>
+        <v>0.09508385352356294</v>
       </c>
       <c r="AE4" t="n">
         <v>0.1047592596323768</v>
@@ -1524,7 +1524,7 @@
         <v>0.05950704156867356</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0669109537630295</v>
+        <v>0.06690228821805841</v>
       </c>
       <c r="AL4" t="n">
         <v>0.001102395605835564</v>
@@ -1569,7 +1569,7 @@
         <v>0.007592359384135709</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003472128413725881</v>
+        <v>0.003465213015290031</v>
       </c>
       <c r="BA4" t="n">
         <v>0.006877520389446929</v>
@@ -1587,7 +1587,7 @@
         <v>0.01166132804576116</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01126068088239815</v>
+        <v>0.01126265850629559</v>
       </c>
       <c r="BG4" t="n">
         <v>0.03120592020388689</v>
@@ -1738,7 +1738,7 @@
         <v>-0.01571709233791745</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.03229166666666663</v>
+        <v>-0.03223684210526312</v>
       </c>
       <c r="S5" t="n">
         <v>0.2022102161100197</v>
@@ -1750,7 +1750,7 @@
         <v>0.1224950884086445</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.001552238805970174</v>
+        <v>-0.001492537313432851</v>
       </c>
       <c r="W5" t="n">
         <v>-0.002686567164179132</v>
@@ -1774,7 +1774,7 @@
         <v>-0.05815324165029466</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.106041257367387</v>
+        <v>-0.106090373280943</v>
       </c>
       <c r="AE5" t="n">
         <v>0.08172888015717096</v>
@@ -1795,7 +1795,7 @@
         <v>-0.02475903614457825</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02259036144578305</v>
+        <v>-0.02253012048192763</v>
       </c>
       <c r="AL5" t="n">
         <v>-0.002048192771084356</v>
@@ -1840,7 +1840,7 @@
         <v>-0.005134328358208973</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.003618421052631537</v>
+        <v>-0.003563596491228027</v>
       </c>
       <c r="BA5" t="n">
         <v>-0.01981927710843374</v>
@@ -1970,7 +1970,7 @@
         <v>-0.008401364982552832</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.009410816152626206</v>
+        <v>-0.009455996875517769</v>
       </c>
       <c r="F6" t="n">
         <v>-0.002511442571751646</v>
@@ -2009,7 +2009,7 @@
         <v>-0.0004651250327311008</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.006480045920420374</v>
+        <v>-0.006455487963642375</v>
       </c>
       <c r="S6" t="n">
         <v>0.3113408526310882</v>
@@ -2021,7 +2021,7 @@
         <v>0.2593206149021527</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0009426425149284629</v>
+        <v>-0.000914716706013033</v>
       </c>
       <c r="W6" t="n">
         <v>-0.0002405130946018103</v>
@@ -2280,7 +2280,7 @@
         <v>0.0006532749873768007</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006467975462080295</v>
+        <v>0.006527676954617612</v>
       </c>
       <c r="S7" t="n">
         <v>0.3540887226082309</v>
@@ -2527,7 +2527,7 @@
         <v>-7.020599769467229e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009200616964809311</v>
+        <v>0.0008832247613139333</v>
       </c>
       <c r="K8" t="n">
         <v>0.02162189054726369</v>
@@ -2542,7 +2542,7 @@
         <v>0.04893246313331234</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04095702156568553</v>
+        <v>0.04097038340427452</v>
       </c>
       <c r="P8" t="n">
         <v>0.05575668708725623</v>
@@ -2783,7 +2783,7 @@
         <v>0.06957236842105266</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06331325301204824</v>
+        <v>0.06337349397590365</v>
       </c>
       <c r="F9" t="n">
         <v>0.03695522388059699</v>
